--- a/data/trans_orig/P6602-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6602-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2007</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2007 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>136177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77649</t>
+          <t>77415</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102337</t>
+          <t>102085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>186001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230999</t>
+          <t>231465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76192</t>
+          <t>76396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>33620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>69136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101328</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157984</t>
+          <t>158505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>137291</t>
+          <t>137293</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180306</t>
+          <t>180773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61570</t>
+          <t>61254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95820</t>
+          <t>93678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395795</t>
+          <t>395326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>464993</t>
+          <t>461075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>390569</t>
+          <t>387201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>433766</t>
+          <t>431696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>800352</t>
+          <t>799118</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>882803</t>
+          <t>880665</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252711</t>
+          <t>251877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>312323</t>
+          <t>308551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96340</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134585</t>
+          <t>134691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359929</t>
+          <t>360813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>431152</t>
+          <t>433068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296551</t>
+          <t>295403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>362287</t>
+          <t>357171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>31235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>53575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334473</t>
+          <t>334974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403896</t>
+          <t>401919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>73802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109602</t>
+          <t>111511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>88836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127871</t>
+          <t>126659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275797</t>
+          <t>274277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311325</t>
+          <t>312839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231337</t>
+          <t>230586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256655</t>
+          <t>256094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517373</t>
+          <t>516690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>560928</t>
+          <t>561035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52847</t>
+          <t>52392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84223</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>47122</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83568</t>
+          <t>83677</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>122996</t>
+          <t>124545</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>49761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>22537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>797723</t>
+          <t>798405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>882002</t>
+          <t>887764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>718098</t>
+          <t>715506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>775235</t>
+          <t>775725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1532701</t>
+          <t>1530439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1644348</t>
+          <t>1638751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>374236</t>
+          <t>374122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>449896</t>
+          <t>444821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198504</t>
+          <t>196179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>534660</t>
+          <t>540036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623910</t>
+          <t>630436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>459004</t>
+          <t>454197</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>534147</t>
+          <t>533957</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85231</t>
+          <t>84907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>517780</t>
+          <t>522576</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>607289</t>
+          <t>607850</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138268</t>
+          <t>138700</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>189433</t>
+          <t>190931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53185</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174086</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229886</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2012</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2012 (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>50084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>66646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100220</t>
+          <t>100713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135264</t>
+          <t>136139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41697</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66267</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49204</t>
+          <t>48331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75030</t>
+          <t>75648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>108424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63933</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>36341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>51582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79246</t>
+          <t>80474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248500</t>
+          <t>253760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>310431</t>
+          <t>313178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>324225</t>
+          <t>323518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>370475</t>
+          <t>372370</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>588209</t>
+          <t>586118</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>667875</t>
+          <t>664870</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229170</t>
+          <t>225570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>281655</t>
+          <t>282053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110729</t>
+          <t>107423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152280</t>
+          <t>151896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348623</t>
+          <t>348485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420143</t>
+          <t>420633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202705</t>
+          <t>202476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257637</t>
+          <t>253100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>58024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246760</t>
+          <t>242666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304223</t>
+          <t>307242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126872</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173973</t>
+          <t>173712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>65698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172108</t>
+          <t>171708</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227129</t>
+          <t>225777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175437</t>
+          <t>172387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212888</t>
+          <t>210592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148357</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178788</t>
+          <t>179081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333852</t>
+          <t>334864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382708</t>
+          <t>383124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91401</t>
+          <t>92129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69515</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110060</t>
+          <t>111389</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>151840</t>
+          <t>154947</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53162</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>64987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>477149</t>
+          <t>476914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>550481</t>
+          <t>551720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>561258</t>
+          <t>562641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>624805</t>
+          <t>623197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1060621</t>
+          <t>1051109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1160338</t>
+          <t>1155554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,02%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349738</t>
+          <t>348476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>417744</t>
+          <t>419431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195465</t>
+          <t>198140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253069</t>
+          <t>251919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>565528</t>
+          <t>562784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>652278</t>
+          <t>650616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>278216</t>
+          <t>278754</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>344006</t>
+          <t>342702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>49071</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78989</t>
+          <t>80413</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>338385</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>410010</t>
+          <t>405177</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>179749</t>
+          <t>180774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235613</t>
+          <t>235954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>52226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>86570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>243430</t>
+          <t>245579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>306980</t>
+          <t>307907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2016</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35154</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>46054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>75818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54088</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>51005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63191</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82669</t>
+          <t>83192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>228102</t>
+          <t>227774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>285439</t>
+          <t>281142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>293181</t>
+          <t>295592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>346179</t>
+          <t>348561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>536565</t>
+          <t>535175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>617249</t>
+          <t>612195</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229521</t>
+          <t>233227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>285088</t>
+          <t>287717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156832</t>
+          <t>155667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202235</t>
+          <t>202841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402993</t>
+          <t>398707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>472777</t>
+          <t>476825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204110</t>
+          <t>206015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257623</t>
+          <t>257009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75752</t>
+          <t>75943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113333</t>
+          <t>112632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292910</t>
+          <t>292673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358499</t>
+          <t>357274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152534</t>
+          <t>151115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>204942</t>
+          <t>203215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>43845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73301</t>
+          <t>73672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207386</t>
+          <t>206575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266034</t>
+          <t>263257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164568</t>
+          <t>164526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202986</t>
+          <t>203033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180769</t>
+          <t>180695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216171</t>
+          <t>214952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356813</t>
+          <t>355298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411197</t>
+          <t>407090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95789</t>
+          <t>95115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131125</t>
+          <t>131366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86027</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>157651</t>
+          <t>159514</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>205076</t>
+          <t>206511</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>47890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45916</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77747</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43706</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>429062</t>
+          <t>428452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>505699</t>
+          <t>503300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>525878</t>
+          <t>524476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>587871</t>
+          <t>588288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>964945</t>
+          <t>975921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1071478</t>
+          <t>1074547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>366717</t>
+          <t>368135</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437024</t>
+          <t>436625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232207</t>
+          <t>229782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288265</t>
+          <t>286017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>614479</t>
+          <t>621362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>706366</t>
+          <t>707314</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269688</t>
+          <t>266339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>333241</t>
+          <t>329381</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105152</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>147246</t>
+          <t>147197</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>385174</t>
+          <t>385768</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>462980</t>
+          <t>463516</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219362</t>
+          <t>214951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278937</t>
+          <t>276609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70452</t>
+          <t>72203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>300129</t>
+          <t>300130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370699</t>
+          <t>370659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2023</t>
+          <t>Población según la exposición a altas/bajas temperaturas en su trabajo en 2023 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42800</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>32703</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220506</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>629335</t>
+          <t>628598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>163968</t>
+          <t>162256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>238376</t>
+          <t>237683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>446063</t>
+          <t>443034</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>875605</t>
+          <t>928343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78201</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283239</t>
+          <t>282919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87232</t>
+          <t>85575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132058</t>
+          <t>132743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169371</t>
+          <t>151477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390701</t>
+          <t>389213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57449</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205254</t>
+          <t>206457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163870</t>
+          <t>153389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121111</t>
+          <t>111826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302707</t>
+          <t>302828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118160</t>
+          <t>120003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47685</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62968</t>
+          <t>57796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148697</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149857</t>
+          <t>149412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182413</t>
+          <t>181586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141357</t>
+          <t>141159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162059</t>
+          <t>161775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299020</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337514</t>
+          <t>337614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65424</t>
+          <t>68025</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62400</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96015</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>36123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>424171</t>
+          <t>424888</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>835686</t>
+          <t>815462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>314475</t>
+          <t>301212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>407674</t>
+          <t>406662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>813189</t>
+          <t>807982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1251149</t>
+          <t>1246379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137657</t>
+          <t>139131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337933</t>
+          <t>339484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175796</t>
+          <t>176373</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>278347</t>
+          <t>265913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>493257</t>
+          <t>499599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84014</t>
+          <t>92728</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>228126</t>
+          <t>226463</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>198811</t>
+          <t>225911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170051</t>
+          <t>175702</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>354000</t>
+          <t>348221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52858</t>
+          <t>54009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141152</t>
+          <t>139587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63792</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96549</t>
+          <t>92811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185723</t>
+          <t>186798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6602-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6602-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100169</t>
+          <t>99927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136177</t>
+          <t>136136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77415</t>
+          <t>77449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102085</t>
+          <t>102919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186001</t>
+          <t>184775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231465</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47117</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76396</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33620</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69136</t>
+          <t>67756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104050</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120253</t>
+          <t>119631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158505</t>
+          <t>156765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>137293</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180773</t>
+          <t>181041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45501</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93678</t>
+          <t>95361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395326</t>
+          <t>398401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>461075</t>
+          <t>465255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>387201</t>
+          <t>388243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>431696</t>
+          <t>431913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>799118</t>
+          <t>798566</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>880665</t>
+          <t>882674</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>251877</t>
+          <t>252590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308551</t>
+          <t>310276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96423</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134691</t>
+          <t>136565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360813</t>
+          <t>359300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433068</t>
+          <t>429209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295403</t>
+          <t>297585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>357171</t>
+          <t>356569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31235</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334974</t>
+          <t>329543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>401919</t>
+          <t>401124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73802</t>
+          <t>72393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111511</t>
+          <t>110151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88836</t>
+          <t>86529</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>126123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274277</t>
+          <t>273973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312839</t>
+          <t>311201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230586</t>
+          <t>231238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256094</t>
+          <t>256358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>516690</t>
+          <t>516516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561035</t>
+          <t>560622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84887</t>
+          <t>85992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>46582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83677</t>
+          <t>84232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>124545</t>
+          <t>123528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49761</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>798405</t>
+          <t>795684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887764</t>
+          <t>884966</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>715506</t>
+          <t>712698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>775725</t>
+          <t>776740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1530439</t>
+          <t>1536867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1638751</t>
+          <t>1643180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>374122</t>
+          <t>374513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>444821</t>
+          <t>446029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196179</t>
+          <t>200366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>540036</t>
+          <t>539441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>630436</t>
+          <t>624917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>454197</t>
+          <t>457831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533957</t>
+          <t>533660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53606</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84907</t>
+          <t>86322</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>522576</t>
+          <t>518971</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>607850</t>
+          <t>605853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138700</t>
+          <t>137682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190931</t>
+          <t>185524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52400</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172386</t>
+          <t>175419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>229125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50084</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66646</t>
+          <t>66202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90360</t>
+          <t>90293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100713</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136139</t>
+          <t>134746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68113</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75648</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108424</t>
+          <t>107881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57646</t>
+          <t>56320</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37440</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>65186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>37044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>61785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80474</t>
+          <t>82060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>253760</t>
+          <t>249864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>313178</t>
+          <t>309795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323518</t>
+          <t>323946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>372370</t>
+          <t>372034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>586118</t>
+          <t>590829</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>664870</t>
+          <t>668256</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>226417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>282053</t>
+          <t>280354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107423</t>
+          <t>111548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151896</t>
+          <t>150790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348485</t>
+          <t>349867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420633</t>
+          <t>416607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202476</t>
+          <t>202520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253100</t>
+          <t>255380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58024</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242666</t>
+          <t>242221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307242</t>
+          <t>302801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128777</t>
+          <t>129718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173712</t>
+          <t>174842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36706</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>63134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>171708</t>
+          <t>170795</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225777</t>
+          <t>224324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172387</t>
+          <t>176739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210592</t>
+          <t>213438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>148433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179081</t>
+          <t>179008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334864</t>
+          <t>334336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>383124</t>
+          <t>383964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92129</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>70151</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111389</t>
+          <t>110111</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154947</t>
+          <t>153150</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52070</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64987</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>476914</t>
+          <t>472838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>551720</t>
+          <t>550896</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>562641</t>
+          <t>560000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>623197</t>
+          <t>623028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1051109</t>
+          <t>1057016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1155554</t>
+          <t>1156802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348476</t>
+          <t>350300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>419431</t>
+          <t>420345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198140</t>
+          <t>196848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251919</t>
+          <t>254309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>562784</t>
+          <t>561939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>650616</t>
+          <t>649313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>278754</t>
+          <t>279460</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>342702</t>
+          <t>342164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80413</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332782</t>
+          <t>335854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>405177</t>
+          <t>408613</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180774</t>
+          <t>179979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235954</t>
+          <t>235974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52226</t>
+          <t>53190</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>84802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245579</t>
+          <t>244326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307907</t>
+          <t>305603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>49395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75818</t>
+          <t>77743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29166</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>50793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39663</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62797</t>
+          <t>62389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83192</t>
+          <t>82410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>227774</t>
+          <t>224919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281142</t>
+          <t>283765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>295592</t>
+          <t>296410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>348561</t>
+          <t>347784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>535175</t>
+          <t>538766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>612195</t>
+          <t>615300</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>233227</t>
+          <t>230299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>287717</t>
+          <t>288622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155667</t>
+          <t>155619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202841</t>
+          <t>204592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398707</t>
+          <t>400508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>476825</t>
+          <t>476676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206015</t>
+          <t>205815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>260746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75943</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112632</t>
+          <t>113534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292673</t>
+          <t>291193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357274</t>
+          <t>356236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151115</t>
+          <t>151996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203215</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43845</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73672</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>206575</t>
+          <t>206784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>263257</t>
+          <t>262474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164526</t>
+          <t>164910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203033</t>
+          <t>204014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180695</t>
+          <t>182762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214952</t>
+          <t>217889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355298</t>
+          <t>355315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407090</t>
+          <t>408594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131366</t>
+          <t>129213</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>55069</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84194</t>
+          <t>86386</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159514</t>
+          <t>160993</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>206511</t>
+          <t>207552</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36719</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47472</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>76551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>45301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>428452</t>
+          <t>426495</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>503300</t>
+          <t>498130</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>524476</t>
+          <t>529422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>588288</t>
+          <t>591648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>975921</t>
+          <t>974082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1074547</t>
+          <t>1070542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>368135</t>
+          <t>367689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436625</t>
+          <t>439416</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229782</t>
+          <t>232795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286017</t>
+          <t>286552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>621362</t>
+          <t>616488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>707314</t>
+          <t>702144</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>266339</t>
+          <t>269102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>329381</t>
+          <t>332668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>107251</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>147197</t>
+          <t>148754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>385768</t>
+          <t>388110</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>463516</t>
+          <t>459183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214951</t>
+          <t>218671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276609</t>
+          <t>276449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>72110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>108269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>300130</t>
+          <t>299077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370659</t>
+          <t>370755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>43359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21550</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>41118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>404111</t>
+          <t>170723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>144309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>628598</t>
+          <t>197656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>212041</t>
+          <t>235204</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162256</t>
+          <t>215787</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237683</t>
+          <t>254791</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>616152</t>
+          <t>405926</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443034</t>
+          <t>372389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>928343</t>
+          <t>440700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>188330</t>
+          <t>202826</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>176583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>282919</t>
+          <t>230722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>112944</t>
+          <t>121775</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85575</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132743</t>
+          <t>138600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>301274</t>
+          <t>324600</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151477</t>
+          <t>293379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>389213</t>
+          <t>357116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>154162</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206457</t>
+          <t>178860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>52750</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45919</t>
+          <t>40729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153389</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>216440</t>
+          <t>206912</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111826</t>
+          <t>180132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302828</t>
+          <t>240575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76255</t>
+          <t>93268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>72563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120003</t>
+          <t>115746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>43274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>56692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111642</t>
+          <t>136542</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>113648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>162133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>440146</t>
+          <t>453002</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440146</t>
+          <t>453002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>440146</t>
+          <t>453002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1245508</t>
+          <t>1073981</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1245508</t>
+          <t>1073981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1245508</t>
+          <t>1073981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>186579</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149412</t>
+          <t>168473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>201227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>152006</t>
+          <t>162769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141159</t>
+          <t>149031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161775</t>
+          <t>173841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>318204</t>
+          <t>349348</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297815</t>
+          <t>327282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337614</t>
+          <t>369741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50794</t>
+          <t>54329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>41361</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68025</t>
+          <t>70133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>33562</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>77556</t>
+          <t>87891</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62406</t>
+          <t>71763</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>94582</t>
+          <t>106762</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>29257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>585150</t>
+          <t>373157</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>424888</t>
+          <t>340519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>815462</t>
+          <t>408817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>379104</t>
+          <t>414603</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>301212</t>
+          <t>392298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>406662</t>
+          <t>437568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>964255</t>
+          <t>787760</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>807982</t>
+          <t>748056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1246379</t>
+          <t>834204</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>255356</t>
+          <t>275802</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139131</t>
+          <t>245125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>339484</t>
+          <t>311289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>156277</t>
+          <t>177068</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>158782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176373</t>
+          <t>197536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>411633</t>
+          <t>452870</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265913</t>
+          <t>415555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>499599</t>
+          <t>491427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92728</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>226463</t>
+          <t>229834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>67722</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>53492</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>225911</t>
+          <t>83724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>266270</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>237098</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>348221</t>
+          <t>299542</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>129559</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>104686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139587</t>
+          <t>157962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>46221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>74759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>150688</t>
+          <t>188828</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92811</t>
+          <t>160400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186798</t>
+          <t>218709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>678335</t>
+          <t>718661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1791170</t>
+          <t>1695727</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1791170</t>
+          <t>1695727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1791170</t>
+          <t>1695727</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
